--- a/data/nzd0483/nzd0483.xlsx
+++ b/data/nzd0483/nzd0483.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E547"/>
+  <dimension ref="A1:E550"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11921,6 +11921,69 @@
       <c r="E547" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:20:39+00:00</t>
+        </is>
+      </c>
+      <c r="B548" t="n">
+        <v>363.54</v>
+      </c>
+      <c r="C548" t="n">
+        <v>371.89</v>
+      </c>
+      <c r="D548" t="n">
+        <v>381.07</v>
+      </c>
+      <c r="E548" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:14:56+00:00</t>
+        </is>
+      </c>
+      <c r="B549" t="n">
+        <v>362.87</v>
+      </c>
+      <c r="C549" t="n">
+        <v>371.52</v>
+      </c>
+      <c r="D549" t="n">
+        <v>380.29</v>
+      </c>
+      <c r="E549" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-23 22:15:01+00:00</t>
+        </is>
+      </c>
+      <c r="B550" t="n">
+        <v>362.79</v>
+      </c>
+      <c r="C550" t="n">
+        <v>370.84</v>
+      </c>
+      <c r="D550" t="n">
+        <v>379.66</v>
+      </c>
+      <c r="E550" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -11935,7 +11998,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B706"/>
+  <dimension ref="A1:B710"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18998,6 +19061,46 @@
       </c>
       <c r="B706" t="n">
         <v>0.74</v>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B707" t="n">
+        <v>-0.9</v>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B708" t="n">
+        <v>-0.58</v>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" t="inlineStr">
+        <is>
+          <t>2025-12-14 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B709" t="n">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" t="inlineStr">
+        <is>
+          <t>2025-12-23 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B710" t="n">
+        <v>-0.33</v>
       </c>
     </row>
   </sheetData>
@@ -19166,28 +19269,28 @@
         <v>0.1368</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2369904052140812</v>
+        <v>-0.2403521722878054</v>
       </c>
       <c r="J2" t="n">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="K2" t="n">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1528503833270594</v>
+        <v>0.1576919952166549</v>
       </c>
       <c r="M2" t="n">
-        <v>2.706054102569111</v>
+        <v>2.703694132488745</v>
       </c>
       <c r="N2" t="n">
-        <v>13.89183725964483</v>
+        <v>13.85905342397222</v>
       </c>
       <c r="O2" t="n">
-        <v>3.727175506954941</v>
+        <v>3.722774962843204</v>
       </c>
       <c r="P2" t="n">
-        <v>372.114309002478</v>
+        <v>372.1543322563219</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -19248,28 +19351,28 @@
         <v>0.0701</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2266088212425885</v>
+        <v>-0.221633827110414</v>
       </c>
       <c r="J3" t="n">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="K3" t="n">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1791415142784929</v>
+        <v>0.1731175611010114</v>
       </c>
       <c r="M3" t="n">
-        <v>2.361206434561568</v>
+        <v>2.369863797050384</v>
       </c>
       <c r="N3" t="n">
-        <v>10.50099007591967</v>
+        <v>10.53782351836043</v>
       </c>
       <c r="O3" t="n">
-        <v>3.240523117633891</v>
+        <v>3.246201398305476</v>
       </c>
       <c r="P3" t="n">
-        <v>373.2093487782923</v>
+        <v>373.1501278444586</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -19330,28 +19433,28 @@
         <v>0.1107</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2393254397766504</v>
+        <v>-0.2331727067495101</v>
       </c>
       <c r="J4" t="n">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="K4" t="n">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2317060991116673</v>
+        <v>0.2216788159371037</v>
       </c>
       <c r="M4" t="n">
-        <v>2.235198177053927</v>
+        <v>2.254305812452605</v>
       </c>
       <c r="N4" t="n">
-        <v>8.475634587392221</v>
+        <v>8.573660300931529</v>
       </c>
       <c r="O4" t="n">
-        <v>2.911294314800931</v>
+        <v>2.928081334411927</v>
       </c>
       <c r="P4" t="n">
-        <v>381.4811503067039</v>
+        <v>381.4079097155607</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -19393,7 +19496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E547"/>
+  <dimension ref="A1:E550"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34165,6 +34268,87 @@
         </is>
       </c>
     </row>
+    <row r="548">
+      <c r="A548" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:20:39+00:00</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>-45.35569620532013,170.85901629798445</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>-45.3560141480997,170.85982749716132</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>-45.356388632364926,170.86058999365778</t>
+        </is>
+      </c>
+      <c r="E548" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:14:56+00:00</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>-45.35570103944138,170.8590111883516</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>-45.35601670013343,170.8598244644761</t>
+        </is>
+      </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>-45.356393747023766,170.86058317637912</t>
+        </is>
+      </c>
+      <c r="E549" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-23 22:15:01+00:00</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>-45.35570161664986,170.85901057824609</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>-45.356021390357355,170.85981889089175</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>-45.35639787809403,170.86057767011474</t>
+        </is>
+      </c>
+      <c r="E550" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0483/nzd0483.xlsx
+++ b/data/nzd0483/nzd0483.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E550"/>
+  <dimension ref="A1:E551"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11984,6 +11984,27 @@
       <c r="E550" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:20:28+00:00</t>
+        </is>
+      </c>
+      <c r="B551" t="n">
+        <v>362.36</v>
+      </c>
+      <c r="C551" t="n">
+        <v>369.93</v>
+      </c>
+      <c r="D551" t="n">
+        <v>378.21</v>
+      </c>
+      <c r="E551" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -11998,7 +12019,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B710"/>
+  <dimension ref="A1:B711"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19101,6 +19122,16 @@
       </c>
       <c r="B710" t="n">
         <v>-0.33</v>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B711" t="n">
+        <v>-0.09</v>
       </c>
     </row>
   </sheetData>
@@ -19269,28 +19300,28 @@
         <v>0.1368</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2403521722878054</v>
+        <v>-0.2417316112713187</v>
       </c>
       <c r="J2" t="n">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="K2" t="n">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1576919952166549</v>
+        <v>0.1595381777881745</v>
       </c>
       <c r="M2" t="n">
-        <v>2.703694132488745</v>
+        <v>2.703893547271258</v>
       </c>
       <c r="N2" t="n">
-        <v>13.85905342397222</v>
+        <v>13.85549050911082</v>
       </c>
       <c r="O2" t="n">
-        <v>3.722774962843204</v>
+        <v>3.722296402640555</v>
       </c>
       <c r="P2" t="n">
-        <v>372.1543322563219</v>
+        <v>372.1707994873674</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -19351,28 +19382,28 @@
         <v>0.0701</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.221633827110414</v>
+        <v>-0.2205881694635017</v>
       </c>
       <c r="J3" t="n">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="K3" t="n">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1731175611010114</v>
+        <v>0.1721621898497566</v>
       </c>
       <c r="M3" t="n">
-        <v>2.369863797050384</v>
+        <v>2.370231526061039</v>
       </c>
       <c r="N3" t="n">
-        <v>10.53782351836043</v>
+        <v>10.53109576057156</v>
       </c>
       <c r="O3" t="n">
-        <v>3.246201398305476</v>
+        <v>3.245164982026578</v>
       </c>
       <c r="P3" t="n">
-        <v>373.1501278444586</v>
+        <v>373.1376451712329</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -19433,28 +19464,28 @@
         <v>0.1107</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2331727067495101</v>
+        <v>-0.2319947233368566</v>
       </c>
       <c r="J4" t="n">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="K4" t="n">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2216788159371037</v>
+        <v>0.2202980436117945</v>
       </c>
       <c r="M4" t="n">
-        <v>2.254305812452605</v>
+        <v>2.256213260907341</v>
       </c>
       <c r="N4" t="n">
-        <v>8.573660300931529</v>
+        <v>8.573849305104739</v>
       </c>
       <c r="O4" t="n">
-        <v>2.928081334411927</v>
+        <v>2.928113608640337</v>
       </c>
       <c r="P4" t="n">
-        <v>381.4079097155607</v>
+        <v>381.3938473864141</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -19496,7 +19527,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E550"/>
+  <dimension ref="A1:E551"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34349,6 +34380,33 @@
         </is>
       </c>
     </row>
+    <row r="551">
+      <c r="A551" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:20:28+00:00</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>-45.35570471914546,170.85900729892893</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>-45.35602766698007,170.85981143212297</t>
+        </is>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>-45.356407386111826,170.86056499696343</t>
+        </is>
+      </c>
+      <c r="E551" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0483/nzd0483.xlsx
+++ b/data/nzd0483/nzd0483.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E551"/>
+  <dimension ref="A1:E552"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12003,6 +12003,27 @@
         <v>378.21</v>
       </c>
       <c r="E551" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-08 22:20:25+00:00</t>
+        </is>
+      </c>
+      <c r="B552" t="n">
+        <v>357.93</v>
+      </c>
+      <c r="C552" t="n">
+        <v>362.52</v>
+      </c>
+      <c r="D552" t="n">
+        <v>369.47</v>
+      </c>
+      <c r="E552" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -12019,7 +12040,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B711"/>
+  <dimension ref="A1:B713"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19132,6 +19153,26 @@
       </c>
       <c r="B711" t="n">
         <v>-0.09</v>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" t="inlineStr">
+        <is>
+          <t>2026-01-31 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B712" t="n">
+        <v>-0.57</v>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" t="inlineStr">
+        <is>
+          <t>2026-02-08 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B713" t="n">
+        <v>0.39</v>
       </c>
     </row>
   </sheetData>
@@ -19300,28 +19341,28 @@
         <v>0.1368</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2417316112713187</v>
+        <v>-0.2448709612195304</v>
       </c>
       <c r="J2" t="n">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="K2" t="n">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1595381777881745</v>
+        <v>0.1624817803904797</v>
       </c>
       <c r="M2" t="n">
-        <v>2.703893547271258</v>
+        <v>2.710683481063969</v>
       </c>
       <c r="N2" t="n">
-        <v>13.85549050911082</v>
+        <v>13.94151825457901</v>
       </c>
       <c r="O2" t="n">
-        <v>3.722296402640555</v>
+        <v>3.733834256441897</v>
       </c>
       <c r="P2" t="n">
-        <v>372.1707994873674</v>
+        <v>372.2084018226191</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -19382,28 +19423,28 @@
         <v>0.0701</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2205881694635017</v>
+        <v>-0.2224996313882263</v>
       </c>
       <c r="J3" t="n">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="K3" t="n">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1721621898497566</v>
+        <v>0.1746466732845263</v>
       </c>
       <c r="M3" t="n">
-        <v>2.370231526061039</v>
+        <v>2.374752351712952</v>
       </c>
       <c r="N3" t="n">
-        <v>10.53109576057156</v>
+        <v>10.55319797792815</v>
       </c>
       <c r="O3" t="n">
-        <v>3.245164982026578</v>
+        <v>3.24856860446692</v>
       </c>
       <c r="P3" t="n">
-        <v>373.1376451712329</v>
+        <v>373.1605401760268</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -19464,28 +19505,28 @@
         <v>0.1107</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2319947233368566</v>
+        <v>-0.2343089039718766</v>
       </c>
       <c r="J4" t="n">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="K4" t="n">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2202980436117945</v>
+        <v>0.2231987037083688</v>
       </c>
       <c r="M4" t="n">
-        <v>2.256213260907341</v>
+        <v>2.261356727519994</v>
       </c>
       <c r="N4" t="n">
-        <v>8.573849305104739</v>
+        <v>8.61869999963732</v>
       </c>
       <c r="O4" t="n">
-        <v>2.928113608640337</v>
+        <v>2.935762251892568</v>
       </c>
       <c r="P4" t="n">
-        <v>381.3938473864141</v>
+        <v>381.421566053497</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -19527,7 +19568,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E551"/>
+  <dimension ref="A1:E552"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34407,6 +34448,33 @@
         </is>
       </c>
     </row>
+    <row r="552">
+      <c r="A552" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-08 22:20:25+00:00</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>-45.35573668205904,170.85897351431487</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>-45.356078776602764,170.8597506963727</t>
+        </is>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>-45.35646469647702,170.86048860836138</t>
+        </is>
+      </c>
+      <c r="E552" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0483/nzd0483.xlsx
+++ b/data/nzd0483/nzd0483.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E552"/>
+  <dimension ref="A1:E555"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12011,21 +12011,84 @@
     <row r="552">
       <c r="A552" s="1" t="inlineStr">
         <is>
-          <t>2026-02-08 22:20:25+00:00</t>
+          <t>2026-02-24 22:20:23+00:00</t>
         </is>
       </c>
       <c r="B552" t="n">
-        <v>357.93</v>
+        <v>360.25</v>
       </c>
       <c r="C552" t="n">
-        <v>362.52</v>
+        <v>368.87</v>
       </c>
       <c r="D552" t="n">
-        <v>369.47</v>
+        <v>377.25</v>
       </c>
       <c r="E552" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:14:31+00:00</t>
+        </is>
+      </c>
+      <c r="B553" t="n">
+        <v>360.32</v>
+      </c>
+      <c r="C553" t="n">
+        <v>368.2</v>
+      </c>
+      <c r="D553" t="n">
+        <v>376.02</v>
+      </c>
+      <c r="E553" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:14:36+00:00</t>
+        </is>
+      </c>
+      <c r="B554" t="n">
+        <v>359.31</v>
+      </c>
+      <c r="C554" t="n">
+        <v>367.52</v>
+      </c>
+      <c r="D554" t="n">
+        <v>375.59</v>
+      </c>
+      <c r="E554" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-20 22:20:18+00:00</t>
+        </is>
+      </c>
+      <c r="B555" t="n">
+        <v>358.55</v>
+      </c>
+      <c r="C555" t="n">
+        <v>366.24</v>
+      </c>
+      <c r="D555" t="n">
+        <v>375.02</v>
+      </c>
+      <c r="E555" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -12040,7 +12103,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B713"/>
+  <dimension ref="A1:B717"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19173,6 +19236,46 @@
       </c>
       <c r="B713" t="n">
         <v>0.39</v>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" t="inlineStr">
+        <is>
+          <t>2026-02-24 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B714" t="n">
+        <v>0.57</v>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B715" t="n">
+        <v>-0.7</v>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B716" t="n">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" t="inlineStr">
+        <is>
+          <t>2026-03-20 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B717" t="n">
+        <v>-0.87</v>
       </c>
     </row>
   </sheetData>
@@ -19341,28 +19444,28 @@
         <v>0.1368</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2448709612195304</v>
+        <v>-0.2514776865104746</v>
       </c>
       <c r="J2" t="n">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="K2" t="n">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1624817803904797</v>
+        <v>0.1699383458661964</v>
       </c>
       <c r="M2" t="n">
-        <v>2.710683481063969</v>
+        <v>2.721133572377966</v>
       </c>
       <c r="N2" t="n">
-        <v>13.94151825457901</v>
+        <v>14.02600510289595</v>
       </c>
       <c r="O2" t="n">
-        <v>3.733834256441897</v>
+        <v>3.745130852573239</v>
       </c>
       <c r="P2" t="n">
-        <v>372.2084018226191</v>
+        <v>372.287889768448</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -19423,28 +19526,28 @@
         <v>0.0701</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2224996313882263</v>
+        <v>-0.2199192643030904</v>
       </c>
       <c r="J3" t="n">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="K3" t="n">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1746466732845263</v>
+        <v>0.1734753996367302</v>
       </c>
       <c r="M3" t="n">
-        <v>2.374752351712952</v>
+        <v>2.359850342414358</v>
       </c>
       <c r="N3" t="n">
-        <v>10.55319797792815</v>
+        <v>10.46310420464549</v>
       </c>
       <c r="O3" t="n">
-        <v>3.24856860446692</v>
+        <v>3.234672194310499</v>
       </c>
       <c r="P3" t="n">
-        <v>373.1605401760268</v>
+        <v>373.1296264695551</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -19505,28 +19608,28 @@
         <v>0.1107</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2343089039718766</v>
+        <v>-0.2308414928920604</v>
       </c>
       <c r="J4" t="n">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="K4" t="n">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2231987037083688</v>
+        <v>0.2211686797102673</v>
       </c>
       <c r="M4" t="n">
-        <v>2.261356727519994</v>
+        <v>2.246564275537406</v>
       </c>
       <c r="N4" t="n">
-        <v>8.61869999963732</v>
+        <v>8.520471857245067</v>
       </c>
       <c r="O4" t="n">
-        <v>2.935762251892568</v>
+        <v>2.918984730560451</v>
       </c>
       <c r="P4" t="n">
-        <v>381.421566053497</v>
+        <v>381.3800079256803</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -19568,7 +19671,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E552"/>
+  <dimension ref="A1:E555"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34451,27 +34554,108 @@
     <row r="552">
       <c r="A552" s="1" t="inlineStr">
         <is>
-          <t>2026-02-08 22:20:25+00:00</t>
+          <t>2026-02-24 22:20:23+00:00</t>
         </is>
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>-45.35573668205904,170.85897351431487</t>
+          <t>-45.35571994301761,170.8589912073907</t>
         </is>
       </c>
       <c r="C552" t="inlineStr">
         <is>
-          <t>-45.356078776602764,170.8597506963727</t>
+          <t>-45.35603497821028,170.85980274388473</t>
         </is>
       </c>
       <c r="D552" t="inlineStr">
         <is>
-          <t>-45.35646469647702,170.86048860836138</t>
+          <t>-45.356413681074514,170.86055660646093</t>
         </is>
       </c>
       <c r="E552" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:14:31+00:00</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>-45.35571943796028,170.85899174123333</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>-45.35603959945919,170.85979725226127</t>
+        </is>
+      </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>-45.3564217464945,170.86054585612686</t>
+        </is>
+      </c>
+      <c r="E553" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:14:36+00:00</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>-45.35572672521579,170.8589840386457</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>-45.356044289681684,170.8597916786724</t>
+        </is>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>-45.356424566112615,170.86054209787926</t>
+        </is>
+      </c>
+      <c r="E554" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-20 22:20:18+00:00</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>-45.35573220869481,170.85897824263787</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>-45.35605311833499,170.85978118720845</t>
+        </is>
+      </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>-45.35642830374571,170.86053711601562</t>
+        </is>
+      </c>
+      <c r="E555" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>

--- a/data/nzd0483/nzd0483.xlsx
+++ b/data/nzd0483/nzd0483.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E555"/>
+  <dimension ref="A1:E559"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12087,6 +12087,90 @@
         <v>375.02</v>
       </c>
       <c r="E555" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:13:58+00:00</t>
+        </is>
+      </c>
+      <c r="B556" t="n">
+        <v>358.48</v>
+      </c>
+      <c r="C556" t="n">
+        <v>365.71</v>
+      </c>
+      <c r="D556" t="n">
+        <v>374.67</v>
+      </c>
+      <c r="E556" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-28 22:20:04+00:00</t>
+        </is>
+      </c>
+      <c r="B557" t="n">
+        <v>356.08</v>
+      </c>
+      <c r="C557" t="n">
+        <v>365.71</v>
+      </c>
+      <c r="D557" t="n">
+        <v>374.67</v>
+      </c>
+      <c r="E557" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-13 22:19:57+00:00</t>
+        </is>
+      </c>
+      <c r="B558" t="n">
+        <v>354.19</v>
+      </c>
+      <c r="C558" t="n">
+        <v>362.96</v>
+      </c>
+      <c r="D558" t="n">
+        <v>372.9</v>
+      </c>
+      <c r="E558" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:14:23+00:00</t>
+        </is>
+      </c>
+      <c r="B559" t="n">
+        <v>354.1</v>
+      </c>
+      <c r="C559" t="n">
+        <v>362.84</v>
+      </c>
+      <c r="D559" t="n">
+        <v>372.37</v>
+      </c>
+      <c r="E559" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -12103,7 +12187,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B717"/>
+  <dimension ref="A1:B723"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19276,6 +19360,66 @@
       </c>
       <c r="B717" t="n">
         <v>-0.87</v>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B718" t="n">
+        <v>-0.67</v>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" t="inlineStr">
+        <is>
+          <t>2026-03-28 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B719" t="n">
+        <v>0.31</v>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" t="inlineStr">
+        <is>
+          <t>2026-04-05 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B720" t="n">
+        <v>-0.39</v>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" t="inlineStr">
+        <is>
+          <t>2026-04-13 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B721" t="n">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B722" t="n">
+        <v>-0.05</v>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B723" t="n">
+        <v>-0.13</v>
       </c>
     </row>
   </sheetData>
@@ -19444,28 +19588,28 @@
         <v>0.1368</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2514776865104746</v>
+        <v>-0.2668972170161982</v>
       </c>
       <c r="J2" t="n">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="K2" t="n">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1699383458661964</v>
+        <v>0.1823087924775503</v>
       </c>
       <c r="M2" t="n">
-        <v>2.721133572377966</v>
+        <v>2.761129292977446</v>
       </c>
       <c r="N2" t="n">
-        <v>14.02600510289595</v>
+        <v>14.63227407587988</v>
       </c>
       <c r="O2" t="n">
-        <v>3.745130852573239</v>
+        <v>3.825215559400525</v>
       </c>
       <c r="P2" t="n">
-        <v>372.287889768448</v>
+        <v>372.4736561328212</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -19526,28 +19670,28 @@
         <v>0.0701</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2199192643030904</v>
+        <v>-0.224564594335061</v>
       </c>
       <c r="J3" t="n">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="K3" t="n">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1734753996367302</v>
+        <v>0.1808043982924163</v>
       </c>
       <c r="M3" t="n">
-        <v>2.359850342414358</v>
+        <v>2.364786446808296</v>
       </c>
       <c r="N3" t="n">
-        <v>10.46310420464549</v>
+        <v>10.46413210678951</v>
       </c>
       <c r="O3" t="n">
-        <v>3.234672194310499</v>
+        <v>3.23483107855565</v>
       </c>
       <c r="P3" t="n">
-        <v>373.1296264695551</v>
+        <v>373.1856080138434</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -19608,28 +19752,28 @@
         <v>0.1107</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2308414928920604</v>
+        <v>-0.2333206534797122</v>
       </c>
       <c r="J4" t="n">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="K4" t="n">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2211686797102673</v>
+        <v>0.2271089263274663</v>
       </c>
       <c r="M4" t="n">
-        <v>2.246564275537406</v>
+        <v>2.24034452494062</v>
       </c>
       <c r="N4" t="n">
-        <v>8.520471857245067</v>
+        <v>8.484621611604833</v>
       </c>
       <c r="O4" t="n">
-        <v>2.918984730560451</v>
+        <v>2.912837381592874</v>
       </c>
       <c r="P4" t="n">
-        <v>381.3800079256803</v>
+        <v>381.4098899794135</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -19671,7 +19815,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E555"/>
+  <dimension ref="A1:E559"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34659,6 +34803,114 @@
         </is>
       </c>
     </row>
+    <row r="556">
+      <c r="A556" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:13:58+00:00</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>-45.355732713752076,170.85897770879498</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>-45.35605677394894,170.8597768430857</t>
+        </is>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>-45.356430598783476,170.8605340569762</t>
+        </is>
+      </c>
+      <c r="E556" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-28 22:20:04+00:00</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>-45.35575002999941,170.85895940560465</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>-45.35605677394894,170.8597768430857</t>
+        </is>
+      </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>-45.356430598783476,170.8605340569762</t>
+        </is>
+      </c>
+      <c r="E557" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-13 22:19:57+00:00</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>-45.35576366654197,170.8589449918343</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>-45.356075741754346,170.8597543028171</t>
+        </is>
+      </c>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>-45.35644220511595,170.86051858697306</t>
+        </is>
+      </c>
+      <c r="E558" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:14:23+00:00</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>-45.35576431590109,170.85894430546412</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>-45.35607656944028,170.8597533192414</t>
+        </is>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>-45.356445680457995,170.86051395471102</t>
+        </is>
+      </c>
+      <c r="E559" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0483/nzd0483.xlsx
+++ b/data/nzd0483/nzd0483.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E559"/>
+  <dimension ref="A1:E565"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12171,6 +12171,132 @@
         <v>372.37</v>
       </c>
       <c r="E559" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:14:08+00:00</t>
+        </is>
+      </c>
+      <c r="B560" t="n">
+        <v>355.22</v>
+      </c>
+      <c r="C560" t="n">
+        <v>363.33</v>
+      </c>
+      <c r="D560" t="n">
+        <v>372.53</v>
+      </c>
+      <c r="E560" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:14:17+00:00</t>
+        </is>
+      </c>
+      <c r="B561" t="n">
+        <v>355.57</v>
+      </c>
+      <c r="C561" t="n">
+        <v>362.73</v>
+      </c>
+      <c r="D561" t="n">
+        <v>372.76</v>
+      </c>
+      <c r="E561" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-07 22:19:58+00:00</t>
+        </is>
+      </c>
+      <c r="B562" t="n">
+        <v>354.92</v>
+      </c>
+      <c r="C562" t="n">
+        <v>362.01</v>
+      </c>
+      <c r="D562" t="n">
+        <v>372.14</v>
+      </c>
+      <c r="E562" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:13:52+00:00</t>
+        </is>
+      </c>
+      <c r="B563" t="n">
+        <v>355.59</v>
+      </c>
+      <c r="C563" t="n">
+        <v>362.42</v>
+      </c>
+      <c r="D563" t="n">
+        <v>372.43</v>
+      </c>
+      <c r="E563" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:19:30+00:00</t>
+        </is>
+      </c>
+      <c r="B564" t="n">
+        <v>356.88</v>
+      </c>
+      <c r="C564" t="n">
+        <v>363.02</v>
+      </c>
+      <c r="D564" t="n">
+        <v>372.57</v>
+      </c>
+      <c r="E564" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:14:01+00:00</t>
+        </is>
+      </c>
+      <c r="B565" t="n">
+        <v>358.04</v>
+      </c>
+      <c r="C565" t="n">
+        <v>363.7</v>
+      </c>
+      <c r="D565" t="n">
+        <v>374.65</v>
+      </c>
+      <c r="E565" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -12187,7 +12313,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B723"/>
+  <dimension ref="A1:B729"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19420,6 +19546,66 @@
       </c>
       <c r="B723" t="n">
         <v>-0.13</v>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B724" t="n">
+        <v>0.31</v>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B725" t="n">
+        <v>-0.59</v>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" t="inlineStr">
+        <is>
+          <t>2026-05-07 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B726" t="n">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B727" t="n">
+        <v>0.29</v>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B728" t="n">
+        <v>-0.45</v>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B729" t="n">
+        <v>-0.84</v>
       </c>
     </row>
   </sheetData>
@@ -19588,28 +19774,28 @@
         <v>0.1368</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2668972170161982</v>
+        <v>-0.2881402411384777</v>
       </c>
       <c r="J2" t="n">
-        <v>558</v>
+        <v>564</v>
       </c>
       <c r="K2" t="n">
-        <v>558</v>
+        <v>564</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1823087924775503</v>
+        <v>0.2002056908705819</v>
       </c>
       <c r="M2" t="n">
-        <v>2.761129292977446</v>
+        <v>2.819412845311221</v>
       </c>
       <c r="N2" t="n">
-        <v>14.63227407587988</v>
+        <v>15.38100213350508</v>
       </c>
       <c r="O2" t="n">
-        <v>3.825215559400525</v>
+        <v>3.921862074768194</v>
       </c>
       <c r="P2" t="n">
-        <v>372.4736561328212</v>
+        <v>372.7303863298008</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -19670,28 +19856,28 @@
         <v>0.0701</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.224564594335061</v>
+        <v>-0.2344267621639956</v>
       </c>
       <c r="J3" t="n">
-        <v>558</v>
+        <v>564</v>
       </c>
       <c r="K3" t="n">
-        <v>558</v>
+        <v>564</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1808043982924163</v>
+        <v>0.1945913904777716</v>
       </c>
       <c r="M3" t="n">
-        <v>2.364786446808296</v>
+        <v>2.38705397187116</v>
       </c>
       <c r="N3" t="n">
-        <v>10.46413210678951</v>
+        <v>10.54828694126617</v>
       </c>
       <c r="O3" t="n">
-        <v>3.23483107855565</v>
+        <v>3.247812639495415</v>
       </c>
       <c r="P3" t="n">
-        <v>373.1856080138434</v>
+        <v>373.3048039710972</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -19752,28 +19938,28 @@
         <v>0.1107</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2333206534797122</v>
+        <v>-0.2386479597169011</v>
       </c>
       <c r="J4" t="n">
-        <v>558</v>
+        <v>564</v>
       </c>
       <c r="K4" t="n">
-        <v>558</v>
+        <v>564</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2271089263274663</v>
+        <v>0.2379624874301371</v>
       </c>
       <c r="M4" t="n">
-        <v>2.24034452494062</v>
+        <v>2.237718436294343</v>
       </c>
       <c r="N4" t="n">
-        <v>8.484621611604833</v>
+        <v>8.457815608652643</v>
       </c>
       <c r="O4" t="n">
-        <v>2.912837381592874</v>
+        <v>2.908232385599996</v>
       </c>
       <c r="P4" t="n">
-        <v>381.4098899794135</v>
+        <v>381.4742680402636</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -19815,7 +20001,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E559"/>
+  <dimension ref="A1:E565"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34911,6 +35097,168 @@
         </is>
       </c>
     </row>
+    <row r="560">
+      <c r="A560" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:14:08+00:00</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>-45.35575623498728,170.8589528469587</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>-45.35607318972262,170.85975733550868</t>
+        </is>
+      </c>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>-45.35644463129816,170.8605153531298</t>
+        </is>
+      </c>
+      <c r="E560" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:14:17+00:00</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>-45.355753709701574,170.85895551617526</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>-45.3560773281524,170.85975241763032</t>
+        </is>
+      </c>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>-45.35644312313085,170.86051736335673</t>
+        </is>
+      </c>
+      <c r="E561" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-07 22:19:58+00:00</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>-45.355758399517846,170.8589505590586</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>-45.35608229426783,170.85974651617533</t>
+        </is>
+      </c>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>-45.356447188625246,170.86051194448393</t>
+        </is>
+      </c>
+      <c r="E562" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:13:52+00:00</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>-45.35575356539953,170.8589556687019</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>-45.35607946634103,170.85974987672623</t>
+        </is>
+      </c>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>-45.356445287023064,170.86051447911808</t>
+        </is>
+      </c>
+      <c r="E563" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:19:30+00:00</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>-45.35574425791733,170.85896550666934</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>-45.35607532791137,170.85975479460495</t>
+        </is>
+      </c>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>-45.35644436900819,170.86051570273452</t>
+        </is>
+      </c>
+      <c r="E564" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:14:01+00:00</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>-45.35573588839766,170.85897435321095</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>-45.35607063769082,170.85976036819997</t>
+        </is>
+      </c>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>-45.35643072992848,170.86053388217394</t>
+        </is>
+      </c>
+      <c r="E565" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0483/nzd0483.xlsx
+++ b/data/nzd0483/nzd0483.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E565"/>
+  <dimension ref="A1:E567"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12297,6 +12297,48 @@
         <v>374.65</v>
       </c>
       <c r="E565" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:13:41+00:00</t>
+        </is>
+      </c>
+      <c r="B566" t="n">
+        <v>359.27</v>
+      </c>
+      <c r="C566" t="n">
+        <v>362.84</v>
+      </c>
+      <c r="D566" t="n">
+        <v>373.36</v>
+      </c>
+      <c r="E566" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:13:59+00:00</t>
+        </is>
+      </c>
+      <c r="B567" t="n">
+        <v>359.79</v>
+      </c>
+      <c r="C567" t="n">
+        <v>362.74</v>
+      </c>
+      <c r="D567" t="n">
+        <v>373.44</v>
+      </c>
+      <c r="E567" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -12313,7 +12355,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B729"/>
+  <dimension ref="A1:B731"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19606,6 +19648,26 @@
       </c>
       <c r="B729" t="n">
         <v>-0.84</v>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B730" t="n">
+        <v>0.63</v>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B731" t="n">
+        <v>-0.71</v>
       </c>
     </row>
   </sheetData>
@@ -19774,28 +19836,28 @@
         <v>0.1368</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2881402411384777</v>
+        <v>-0.2923031598443848</v>
       </c>
       <c r="J2" t="n">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="K2" t="n">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2002056908705819</v>
+        <v>0.2049741459847265</v>
       </c>
       <c r="M2" t="n">
-        <v>2.819412845311221</v>
+        <v>2.827177013023683</v>
       </c>
       <c r="N2" t="n">
-        <v>15.38100213350508</v>
+        <v>15.43177403679145</v>
       </c>
       <c r="O2" t="n">
-        <v>3.921862074768194</v>
+        <v>3.928329675166208</v>
       </c>
       <c r="P2" t="n">
-        <v>372.7303863298008</v>
+        <v>372.7808988389656</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -19856,28 +19918,28 @@
         <v>0.0701</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2344267621639956</v>
+        <v>-0.2376442671722434</v>
       </c>
       <c r="J3" t="n">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="K3" t="n">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1945913904777716</v>
+        <v>0.1991744644104925</v>
       </c>
       <c r="M3" t="n">
-        <v>2.38705397187116</v>
+        <v>2.39416388167683</v>
       </c>
       <c r="N3" t="n">
-        <v>10.54828694126617</v>
+        <v>10.57366648089913</v>
       </c>
       <c r="O3" t="n">
-        <v>3.247812639495415</v>
+        <v>3.25171746633977</v>
       </c>
       <c r="P3" t="n">
-        <v>373.3048039710972</v>
+        <v>373.3438458615012</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -19938,28 +20000,28 @@
         <v>0.1107</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2386479597169011</v>
+        <v>-0.239926031580296</v>
       </c>
       <c r="J4" t="n">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="K4" t="n">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2379624874301371</v>
+        <v>0.2410909140717893</v>
       </c>
       <c r="M4" t="n">
-        <v>2.237718436294343</v>
+        <v>2.234831297060412</v>
       </c>
       <c r="N4" t="n">
-        <v>8.457815608652643</v>
+        <v>8.437821214131525</v>
       </c>
       <c r="O4" t="n">
-        <v>2.908232385599996</v>
+        <v>2.90479280055076</v>
       </c>
       <c r="P4" t="n">
-        <v>381.4742680402636</v>
+        <v>381.4897762016926</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -20001,7 +20063,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E565"/>
+  <dimension ref="A1:E567"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35259,6 +35321,60 @@
         </is>
       </c>
     </row>
+    <row r="566">
+      <c r="A566" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:13:41+00:00</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>-45.355727013819966,170.8589837335927</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>-45.35607656944028,170.8597533192414</t>
+        </is>
+      </c>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>-45.35643918878116,170.86052260742647</t>
+        </is>
+      </c>
+      <c r="E566" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:13:59+00:00</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>-45.35572326196572,170.85898769928167</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>-45.35607725917857,170.85975249959495</t>
+        </is>
+      </c>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>-45.35643866420119,170.8605233066357</t>
+        </is>
+      </c>
+      <c r="E567" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
